--- a/Models/Верблюды/results/Верблюды - Результаты прогнозов ХВ средние.xlsx
+++ b/Models/Верблюды/results/Верблюды - Результаты прогнозов ХВ средние.xlsx
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="C2" t="n">
         <v>0.11</v>
@@ -471,13 +471,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.54</v>
+        <v>5.03</v>
       </c>
       <c r="C3" t="n">
-        <v>3.83</v>
+        <v>4.04</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="4">
@@ -487,13 +487,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.67</v>
+        <v>15.92</v>
       </c>
       <c r="C4" t="n">
-        <v>9.359999999999999</v>
+        <v>13.73</v>
       </c>
       <c r="D4" t="n">
-        <v>69.73</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="5">
@@ -503,13 +503,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>62.88</v>
+        <v>107.89</v>
       </c>
       <c r="C5" t="n">
-        <v>46.21</v>
+        <v>75.17</v>
       </c>
       <c r="D5" t="n">
-        <v>11.05</v>
+        <v>13.84</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.66</v>
+        <v>1.41</v>
       </c>
       <c r="C6" t="n">
-        <v>0.54</v>
+        <v>1.11</v>
       </c>
       <c r="D6" t="inlineStr"/>
     </row>
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="C8" t="n">
         <v>0.03</v>
@@ -575,13 +575,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.98</v>
+        <v>2.39</v>
       </c>
       <c r="C10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>9.039999999999999</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="11">
@@ -591,13 +591,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="C11" t="n">
-        <v>1.69</v>
+        <v>1.22</v>
       </c>
       <c r="D11" t="n">
-        <v>13.07</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -607,10 +607,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.55</v>
+        <v>3.14</v>
       </c>
       <c r="C12" t="n">
-        <v>1.03</v>
+        <v>2.04</v>
       </c>
       <c r="D12" t="inlineStr"/>
     </row>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="C13" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="D13" t="inlineStr"/>
     </row>
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87.62</v>
+        <v>198.88</v>
       </c>
       <c r="C14" t="n">
-        <v>60.71</v>
+        <v>126.7</v>
       </c>
       <c r="D14" t="n">
-        <v>192.84</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="15">
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>128.85</v>
+        <v>143.84</v>
       </c>
       <c r="C15" t="n">
-        <v>96.28</v>
+        <v>115.97</v>
       </c>
       <c r="D15" t="n">
-        <v>24.7</v>
+        <v>32.34</v>
       </c>
     </row>
     <row r="16">
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="D16" t="inlineStr"/>
     </row>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.62</v>
+        <v>4.59</v>
       </c>
       <c r="C17" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="D17" t="inlineStr"/>
     </row>
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C18" t="n">
         <v>0.02</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.01</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="D19" t="inlineStr"/>
     </row>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>45.95</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>34.43</v>
+        <v>58.47</v>
       </c>
       <c r="D21" t="n">
-        <v>18.85</v>
+        <v>20.88</v>
       </c>
     </row>
   </sheetData>
